--- a/public/frontend/exportsamples/userssample.xlsx
+++ b/public/frontend/exportsamples/userssample.xlsx
@@ -1,28 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10118"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/MAMP/htdocs/gsf/public/frontend/exportsamples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23EC9D74-AE58-489B-B33B-AE1CE4C3111D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B795AAD5-CEA9-D248-93FD-8E6AB2C1CB19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="19420" windowHeight="10540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" forceFullCalc="1"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -30,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>Male</t>
   </si>
@@ -44,9 +47,6 @@
     <t>Phone</t>
   </si>
   <si>
-    <t>Sex</t>
-  </si>
-  <si>
     <t>David Oghi</t>
   </si>
   <si>
@@ -59,9 +59,6 @@
     <t>Sarah Akande Ajiboye</t>
   </si>
   <si>
-    <t>role</t>
-  </si>
-  <si>
     <t>portfolio_session</t>
   </si>
   <si>
@@ -86,9 +83,6 @@
     <t>twitter</t>
   </si>
   <si>
-    <t>Member</t>
-  </si>
-  <si>
     <t>2018/2019</t>
   </si>
   <si>
@@ -101,9 +95,6 @@
     <t>saa@gmail.com</t>
   </si>
   <si>
-    <t>Publicity Secretary</t>
-  </si>
-  <si>
     <t>2019/2020</t>
   </si>
   <si>
@@ -144,13 +135,16 @@
   </si>
   <si>
     <t>OND</t>
+  </si>
+  <si>
+    <t>Gender</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -161,15 +155,24 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -193,7 +196,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -203,6 +206,7 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -225,13 +229,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>6350</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>50800</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
@@ -332,21 +336,6 @@
           <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
         </a:p>
         <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
-            <a:t>If the role is an Executive, we expect the academic session of service in the portfolio_session column, e.g 2020/2021</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="1" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
-            <a:t>If the role is a member, portfolio_session can be left empty</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
           <a:endParaRPr lang="en-US" sz="1100" b="1" baseline="0"/>
         </a:p>
         <a:p>
@@ -368,9 +357,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -408,9 +397,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -443,26 +432,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -495,26 +467,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -688,21 +643,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.26953125" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="7" width="17.81640625" customWidth="1"/>
-    <col min="8" max="8" width="11.81640625" customWidth="1"/>
-    <col min="9" max="9" width="11.81640625" style="2" customWidth="1"/>
-    <col min="10" max="11" width="10.26953125" style="3" customWidth="1"/>
-    <col min="12" max="12" width="15.453125" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" customWidth="1"/>
+    <col min="5" max="6" width="17.83203125" customWidth="1"/>
+    <col min="7" max="7" width="11.83203125" customWidth="1"/>
+    <col min="8" max="8" width="11.83203125" style="2" customWidth="1"/>
+    <col min="9" max="10" width="10.33203125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -712,136 +666,124 @@
       <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
-        <v>4</v>
+      <c r="D1" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="E1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F1" t="s">
         <v>10</v>
       </c>
       <c r="G1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N1" t="s">
+    </row>
+    <row r="2" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="29">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
         <v>0</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="29">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="D3" t="s">
         <v>0</v>
       </c>
       <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L4">
+      <c r="K4">
         <v>5</v>
       </c>
     </row>
